--- a/StructureDefinition-ischemic-stroke-etiology-ext.xlsx
+++ b/StructureDefinition-ischemic-stroke-etiology-ext.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-07T11:15:53+00:00</t>
+    <t>2026-05-08T09:03:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ischemic-stroke-etiology-ext.xlsx
+++ b/StructureDefinition-ischemic-stroke-etiology-ext.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-08T09:03:17+00:00</t>
+    <t>2026-05-08T09:31:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ischemic-stroke-etiology-ext.xlsx
+++ b/StructureDefinition-ischemic-stroke-etiology-ext.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-08T09:31:23+00:00</t>
+    <t>2026-05-08T10:13:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ischemic-stroke-etiology-ext.xlsx
+++ b/StructureDefinition-ischemic-stroke-etiology-ext.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-08T10:13:17+00:00</t>
+    <t>2026-05-11T15:54:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ischemic-stroke-etiology-ext.xlsx
+++ b/StructureDefinition-ischemic-stroke-etiology-ext.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-11T15:54:34+00:00</t>
+    <t>2026-05-11T15:54:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ischemic-stroke-etiology-ext.xlsx
+++ b/StructureDefinition-ischemic-stroke-etiology-ext.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-11T15:54:44+00:00</t>
+    <t>2026-05-12T07:59:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ischemic-stroke-etiology-ext.xlsx
+++ b/StructureDefinition-ischemic-stroke-etiology-ext.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-12T07:59:38+00:00</t>
+    <t>2026-05-12T09:41:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ischemic-stroke-etiology-ext.xlsx
+++ b/StructureDefinition-ischemic-stroke-etiology-ext.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-12T09:41:56+00:00</t>
+    <t>2026-05-12T11:55:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ischemic-stroke-etiology-ext.xlsx
+++ b/StructureDefinition-ischemic-stroke-etiology-ext.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-12T11:55:23+00:00</t>
+    <t>2026-05-13T14:14:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ischemic-stroke-etiology-ext.xlsx
+++ b/StructureDefinition-ischemic-stroke-etiology-ext.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-13T14:14:43+00:00</t>
+    <t>2026-05-13T15:23:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ischemic-stroke-etiology-ext.xlsx
+++ b/StructureDefinition-ischemic-stroke-etiology-ext.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-13T15:23:44+00:00</t>
+    <t>2026-05-14T08:09:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ischemic-stroke-etiology-ext.xlsx
+++ b/StructureDefinition-ischemic-stroke-etiology-ext.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-14T08:09:55+00:00</t>
+    <t>2026-05-14T08:55:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ischemic-stroke-etiology-ext.xlsx
+++ b/StructureDefinition-ischemic-stroke-etiology-ext.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-14T08:55:50+00:00</t>
+    <t>2026-05-14T09:35:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ischemic-stroke-etiology-ext.xlsx
+++ b/StructureDefinition-ischemic-stroke-etiology-ext.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-14T09:35:04+00:00</t>
+    <t>2026-05-14T11:02:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ischemic-stroke-etiology-ext.xlsx
+++ b/StructureDefinition-ischemic-stroke-etiology-ext.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-14T11:02:20+00:00</t>
+    <t>2026-05-15T10:10:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ischemic-stroke-etiology-ext.xlsx
+++ b/StructureDefinition-ischemic-stroke-etiology-ext.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-15T10:10:20+00:00</t>
+    <t>2026-06-01T07:47:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ischemic-stroke-etiology-ext.xlsx
+++ b/StructureDefinition-ischemic-stroke-etiology-ext.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T07:47:29+00:00</t>
+    <t>2026-06-01T10:24:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ischemic-stroke-etiology-ext.xlsx
+++ b/StructureDefinition-ischemic-stroke-etiology-ext.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T10:24:12+00:00</t>
+    <t>2026-06-01T10:42:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ischemic-stroke-etiology-ext.xlsx
+++ b/StructureDefinition-ischemic-stroke-etiology-ext.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T10:42:50+00:00</t>
+    <t>2026-06-01T12:57:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ischemic-stroke-etiology-ext.xlsx
+++ b/StructureDefinition-ischemic-stroke-etiology-ext.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T12:57:35+00:00</t>
+    <t>2026-06-02T10:42:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ischemic-stroke-etiology-ext.xlsx
+++ b/StructureDefinition-ischemic-stroke-etiology-ext.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-02T10:42:43+00:00</t>
+    <t>2026-06-03T07:55:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ischemic-stroke-etiology-ext.xlsx
+++ b/StructureDefinition-ischemic-stroke-etiology-ext.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-03T07:55:03+00:00</t>
+    <t>2026-06-03T14:48:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ischemic-stroke-etiology-ext.xlsx
+++ b/StructureDefinition-ischemic-stroke-etiology-ext.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-03T14:48:08+00:00</t>
+    <t>2026-06-03T14:50:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ischemic-stroke-etiology-ext.xlsx
+++ b/StructureDefinition-ischemic-stroke-etiology-ext.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-03T14:50:23+00:00</t>
+    <t>2026-06-08T09:55:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ischemic-stroke-etiology-ext.xlsx
+++ b/StructureDefinition-ischemic-stroke-etiology-ext.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-08T09:55:23+00:00</t>
+    <t>2026-06-08T10:51:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ischemic-stroke-etiology-ext.xlsx
+++ b/StructureDefinition-ischemic-stroke-etiology-ext.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-08T10:51:55+00:00</t>
+    <t>2026-06-08T11:21:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ischemic-stroke-etiology-ext.xlsx
+++ b/StructureDefinition-ischemic-stroke-etiology-ext.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-08T11:21:15+00:00</t>
+    <t>2026-06-11T11:47:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Etiology of ischemic stroke when known.</t>
+    <t>Etiology of ischemic stroke, including undetermined when the etiology is not known.</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/StructureDefinition-ischemic-stroke-etiology-ext.xlsx
+++ b/StructureDefinition-ischemic-stroke-etiology-ext.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-11T11:47:40+00:00</t>
+    <t>2026-06-11T14:44:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ischemic-stroke-etiology-ext.xlsx
+++ b/StructureDefinition-ischemic-stroke-etiology-ext.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-11T14:44:28+00:00</t>
+    <t>2026-06-12T09:34:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ischemic-stroke-etiology-ext.xlsx
+++ b/StructureDefinition-ischemic-stroke-etiology-ext.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T09:34:13+00:00</t>
+    <t>2026-07-01T13:43:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ischemic-stroke-etiology-ext.xlsx
+++ b/StructureDefinition-ischemic-stroke-etiology-ext.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T13:43:23+00:00</t>
+    <t>2026-07-09T09:09:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ischemic-stroke-etiology-ext.xlsx
+++ b/StructureDefinition-ischemic-stroke-etiology-ext.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-09T09:09:43+00:00</t>
+    <t>2026-07-13T09:21:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ischemic-stroke-etiology-ext.xlsx
+++ b/StructureDefinition-ischemic-stroke-etiology-ext.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-13T09:21:26+00:00</t>
+    <t>2026-07-13T09:30:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ischemic-stroke-etiology-ext.xlsx
+++ b/StructureDefinition-ischemic-stroke-etiology-ext.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-13T09:30:27+00:00</t>
+    <t>2026-07-14T07:23:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ischemic-stroke-etiology-ext.xlsx
+++ b/StructureDefinition-ischemic-stroke-etiology-ext.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-14T07:23:58+00:00</t>
+    <t>2026-07-17T09:40:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ischemic-stroke-etiology-ext.xlsx
+++ b/StructureDefinition-ischemic-stroke-etiology-ext.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-17T09:40:30+00:00</t>
+    <t>2026-07-21T08:04:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ischemic-stroke-etiology-ext.xlsx
+++ b/StructureDefinition-ischemic-stroke-etiology-ext.xlsx
@@ -27,7 +27,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://tecnomod-um.org/StructureDefinition/ischemic-stroke-etiology-ext</t>
+    <t>http://qualityregistry.org/StructureDefinition/ischemic-stroke-etiology-ext</t>
   </si>
   <si>
     <t>Version</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T08:04:16+00:00</t>
+    <t>2026-08-31T09:17:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -72,7 +72,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>Tecnomod / Universidad de Murcia (http://tecnomod-um.org)</t>
+    <t>Tecnomod / Universidad de Murcia (http://qualityregistry.org)</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -350,7 +350,7 @@
     <t>required</t>
   </si>
   <si>
-    <t>http://tecnomod-um.org/ValueSet/stroke-etiology-vs</t>
+    <t>http://qualityregistry.org/ValueSet/stroke-etiology-vs</t>
   </si>
   <si>
     <t xml:space="preserve">ext-1
@@ -711,7 +711,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="18.49609375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="41.99609375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="42.44140625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>

--- a/StructureDefinition-ischemic-stroke-etiology-ext.xlsx
+++ b/StructureDefinition-ischemic-stroke-etiology-ext.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T09:17:06+00:00</t>
+    <t>2026-08-31T10:08:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ischemic-stroke-etiology-ext.xlsx
+++ b/StructureDefinition-ischemic-stroke-etiology-ext.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T10:08:26+00:00</t>
+    <t>2026-09-04T09:44:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ischemic-stroke-etiology-ext.xlsx
+++ b/StructureDefinition-ischemic-stroke-etiology-ext.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T09:44:50+00:00</t>
+    <t>2026-09-04T10:11:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
